--- a/hojun-w5t8/Hojun_My_Expressions.xlsx
+++ b/hojun-w5t8/Hojun_My_Expressions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="My Expressions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'My Expressions'!$A$1:$D$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2574,8 +2574,312 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>I'd go with ~ because ~</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>저라면 ~요, 왜냐하면 ~</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>What draws me to ~ is ~</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>~에 끌리는 이유는 ~</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>The tricky part would be ~</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>까다로운 건 ~일 거예요</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Compared to ~, ~ is ~</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>~에 비하면 ~는 ~</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Singapore -&gt; maritime structure</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>used Caisson</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>had a similar experience for domestic project Kuwait -&gt; first big project when I joined</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>his team members joined this project</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>artificial island</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Jang Bogo project done by the another division</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>HDEC done the high-speed railway bridge for KTX, SRT</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>building a bridge is the beauty of civil engeering</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>I’d go with USA, Singapore because it is good place to learn English</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>What draws me to countries like USA and Singapore is that these two are good for work and living with family</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>The tricky part would be English communication. Explaining design over to agencies</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Class 10</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>업계 특수</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>The biggest difference is the turbine. Offshore wind project is being influenced by the turbine supplier</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D100"/>
+  <autoFilter ref="A1:D116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>